--- a/structure-pages/ig/CdaToOrganisationConceptMap.xlsx
+++ b/structure-pages/ig/CdaToOrganisationConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:38:30+00:00</t>
+    <t>2026-03-23T12:01:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
